--- a/out_hist/pedimentos.xlsx
+++ b/out_hist/pedimentos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Expedientes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expedientes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N819"/>
+  <dimension ref="A1:N836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -42728,11 +42728,11 @@
       </c>
       <c r="G817" t="inlineStr">
         <is>
-          <t>Edicto de mensura (x2)</t>
+          <t>Edicto de mensura (x3)</t>
         </is>
       </c>
       <c r="H817" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I817" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>NEVADA ll</t>
+          <t>NEVADA II</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -42787,11 +42787,11 @@
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>Edicto de mensura (x2)</t>
+          <t>Edicto de mensura (x3)</t>
         </is>
       </c>
       <c r="H818" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I818" t="inlineStr">
         <is>
@@ -42846,11 +42846,11 @@
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>Edicto de mensura (x1)</t>
+          <t>Edicto de mensura (x3)</t>
         </is>
       </c>
       <c r="H819" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I819" t="inlineStr">
         <is>
@@ -42870,6 +42870,919 @@
         <v>-69.673497</v>
       </c>
       <c r="N819" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>1124-000373-B-10</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Bastias Hugo Enrique</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>MARIA</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr"/>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Iglesia</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x3)</t>
+        </is>
+      </c>
+      <c r="H820" t="n">
+        <v>3</v>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K820" t="n">
+        <v>6</v>
+      </c>
+      <c r="L820" t="n">
+        <v>-30.037534</v>
+      </c>
+      <c r="M820" t="n">
+        <v>-69.06965099999999</v>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>1124-212-0-2024</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>GRUPO IDAHO S.A.S</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>bentonita</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Calingasta</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>Manifestación de descubrimiento (x1); Edicto de mensura (x2)</t>
+        </is>
+      </c>
+      <c r="H821" t="n">
+        <v>3</v>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K821" t="n">
+        <v>1</v>
+      </c>
+      <c r="L821" t="n">
+        <v>-31.625504</v>
+      </c>
+      <c r="M821" t="n">
+        <v>-69.444969</v>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>1124-224-E-25</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Elizondo Juan Carlos</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr"/>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>Albardón</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Otro / sin clasificar</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>Otro / sin clasificar (x3)</t>
+        </is>
+      </c>
+      <c r="H822" t="n">
+        <v>3</v>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K822" t="n">
+        <v>4</v>
+      </c>
+      <c r="L822" t="n">
+        <v>-31.454897</v>
+      </c>
+      <c r="M822" t="n">
+        <v>-68.55168999999999</v>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>1124-307-B-2024</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>GABRIEL ENRIQUE BASTIAS</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>oro</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>Calingasta</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x3)</t>
+        </is>
+      </c>
+      <c r="H823" t="n">
+        <v>3</v>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K823" t="n">
+        <v>1</v>
+      </c>
+      <c r="L823" t="n">
+        <v>-30.912419</v>
+      </c>
+      <c r="M823" t="n">
+        <v>-69.60906799999999</v>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>1124-333-D-24</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Dirección Provincial de Vialidad</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr"/>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>San Martín</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x3)</t>
+        </is>
+      </c>
+      <c r="H824" t="n">
+        <v>3</v>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="K824" t="n">
+        <v>4</v>
+      </c>
+      <c r="L824" t="n">
+        <v>-31.527273</v>
+      </c>
+      <c r="M824" t="n">
+        <v>-68.419386</v>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>1118-R-96</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Minera Peregrine Argentina S.A.U</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>PAMPA</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr"/>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>Calingasta</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x3)</t>
+        </is>
+      </c>
+      <c r="H825" t="n">
+        <v>3</v>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K825" t="n">
+        <v>5</v>
+      </c>
+      <c r="L825" t="n">
+        <v>-31.536724</v>
+      </c>
+      <c r="M825" t="n">
+        <v>-70.479297</v>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>1124-000256-2020</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>LP E.E.M</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>RA 1</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr"/>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Calingasta</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x1)</t>
+        </is>
+      </c>
+      <c r="H826" t="n">
+        <v>1</v>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K826" t="n">
+        <v>6</v>
+      </c>
+      <c r="L826" t="n">
+        <v>-31.211437</v>
+      </c>
+      <c r="M826" t="n">
+        <v>-70.29287100000001</v>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>1124-217-B-22</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Bosque Hugo Arturo</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>MABEL 1</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr"/>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Calingasta</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x3)</t>
+        </is>
+      </c>
+      <c r="H827" t="n">
+        <v>3</v>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>2026-08, 2026-09</t>
+        </is>
+      </c>
+      <c r="K827" t="n">
+        <v>4</v>
+      </c>
+      <c r="L827" t="n">
+        <v>-30.553509</v>
+      </c>
+      <c r="M827" t="n">
+        <v>-70.130916</v>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>1124-231-B-2023</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>“BENEGAS DIEGO ARMANDO</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>cuarzo</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Valle Fértil</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Otro / sin clasificar</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>Otro / sin clasificar (x1)</t>
+        </is>
+      </c>
+      <c r="H828" t="n">
+        <v>1</v>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K828" t="n">
+        <v>1</v>
+      </c>
+      <c r="L828" t="n">
+        <v>-30.619303</v>
+      </c>
+      <c r="M828" t="n">
+        <v>-67.613074</v>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>1124-385-E-15</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Elizondo Dina Myriam</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>ESPERANZA</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr"/>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Calingasta</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x3)</t>
+        </is>
+      </c>
+      <c r="H829" t="n">
+        <v>3</v>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>2026-08, 2026-09</t>
+        </is>
+      </c>
+      <c r="K829" t="n">
+        <v>4</v>
+      </c>
+      <c r="L829" t="n">
+        <v>-30.894759</v>
+      </c>
+      <c r="M829" t="n">
+        <v>-70.23393</v>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>1124-591-A-25</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>GOLDEN MINING S$.A</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>oro</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Caucete</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Permiso de cateo / exploración</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>Permiso de cateo / exploración (x3)</t>
+        </is>
+      </c>
+      <c r="H830" t="n">
+        <v>3</v>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K830" t="n">
+        <v>3</v>
+      </c>
+      <c r="L830" t="n">
+        <v>-31.555908</v>
+      </c>
+      <c r="M830" t="n">
+        <v>-67.473074</v>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>1124-610-G-2024</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>GOLDEN MINING $.A</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>EXPTE</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>oro</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Calingasta</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x2)</t>
+        </is>
+      </c>
+      <c r="H831" t="n">
+        <v>2</v>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K831" t="n">
+        <v>2</v>
+      </c>
+      <c r="L831" t="n">
+        <v>-30.645338</v>
+      </c>
+      <c r="M831" t="n">
+        <v>-68.85939500000001</v>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>1124-612-G-2024</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>GOLDEN MINING S.A</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>oro</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Ullum</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x1)</t>
+        </is>
+      </c>
+      <c r="H832" t="n">
+        <v>1</v>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K832" t="n">
+        <v>1</v>
+      </c>
+      <c r="L832" t="n">
+        <v>-30.673211</v>
+      </c>
+      <c r="M832" t="n">
+        <v>-68.83899599999999</v>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>1124-634-F-23</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Filo del Sol Exploraciones S.A</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr"/>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Iglesia</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Servidumbre minera</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>Servidumbre minera (x2)</t>
+        </is>
+      </c>
+      <c r="H833" t="n">
+        <v>2</v>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K833" t="n">
+        <v>4</v>
+      </c>
+      <c r="L833" t="n">
+        <v>-28.510013</v>
+      </c>
+      <c r="M833" t="n">
+        <v>-69.577395</v>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>1124-649-E-241</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Epitermal S.A</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>cuarzo</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Albardón</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Permiso de cateo / exploración</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>Permiso de cateo / exploración (x2)</t>
+        </is>
+      </c>
+      <c r="H834" t="n">
+        <v>2</v>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K834" t="n">
+        <v>1</v>
+      </c>
+      <c r="L834" t="n">
+        <v>-30.619303</v>
+      </c>
+      <c r="M834" t="n">
+        <v>-67.613074</v>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>338.682-1-92</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>RA 1</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr"/>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Calingasta</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x1)</t>
+        </is>
+      </c>
+      <c r="H835" t="n">
+        <v>1</v>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="K835" t="n">
+        <v>7</v>
+      </c>
+      <c r="L835" t="n">
+        <v>-31.210994</v>
+      </c>
+      <c r="M835" t="n">
+        <v>-70.295795</v>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>583-R-95</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Darío Becerra, Paz Eric Martín</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>LOS CRISOLES 3</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr"/>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Iglesia</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x3)</t>
+        </is>
+      </c>
+      <c r="H836" t="n">
+        <v>3</v>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K836" t="n">
+        <v>5</v>
+      </c>
+      <c r="L836" t="n">
+        <v>-29.760661</v>
+      </c>
+      <c r="M836" t="n">
+        <v>-69.67442699999999</v>
+      </c>
+      <c r="N836" t="inlineStr">
         <is>
           <t>posgar2007</t>
         </is>

--- a/out_hist/pedimentos.xlsx
+++ b/out_hist/pedimentos.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N836"/>
+  <dimension ref="A1:N837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -43736,23 +43736,23 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>583-R-95</t>
+          <t>1124-242-H-13</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Darío Becerra, Paz Eric Martín</t>
+          <t>Moncho Juan Jose y Alonso manuel Domingo</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>LOS CRISOLES 3</t>
+          <t>MARTINA</t>
         </is>
       </c>
       <c r="D836" t="inlineStr"/>
       <c r="E836" t="inlineStr">
         <is>
-          <t>Iglesia</t>
+          <t>Calingasta</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
@@ -43762,11 +43762,11 @@
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>Edicto de mensura (x3)</t>
+          <t>Edicto de mensura (x1)</t>
         </is>
       </c>
       <c r="H836" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I836" t="inlineStr">
         <is>
@@ -43777,12 +43777,67 @@
         <v>5</v>
       </c>
       <c r="L836" t="n">
+        <v>-31.096375</v>
+      </c>
+      <c r="M836" t="n">
+        <v>-69.73417999999999</v>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>posgar2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>583-R-95</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Darío Becerra, Paz Eric Martín</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>LOS CRISOLES 3</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr"/>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Iglesia</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Edicto de mensura</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>Edicto de mensura (x3)</t>
+        </is>
+      </c>
+      <c r="H837" t="n">
+        <v>3</v>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="K837" t="n">
+        <v>5</v>
+      </c>
+      <c r="L837" t="n">
         <v>-29.760661</v>
       </c>
-      <c r="M836" t="n">
+      <c r="M837" t="n">
         <v>-69.67442699999999</v>
       </c>
-      <c r="N836" t="inlineStr">
+      <c r="N837" t="inlineStr">
         <is>
           <t>posgar2007</t>
         </is>
